--- a/src/assets/example/test.xlsx
+++ b/src/assets/example/test.xlsx
@@ -4,11 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="21900" activeTab="1"/>
+    <workbookView windowHeight="21900"/>
   </bookViews>
   <sheets>
     <sheet name="区域销售" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,136 +27,47 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>月份</t>
   </si>
   <si>
-    <t>华东</t>
+    <t>示例字段1</t>
   </si>
   <si>
-    <t>华南</t>
+    <t>示例字段2</t>
   </si>
   <si>
-    <t>华西</t>
-  </si>
-  <si>
-    <t>华北</t>
-  </si>
-  <si>
-    <t>填报日期</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>2026-01</t>
-  </si>
-  <si>
-    <t>春节前备货带动华东销售</t>
-  </si>
-  <si>
-    <t>2026-02</t>
-  </si>
-  <si>
-    <t>线上促销活动启动</t>
+    <t>示例字段3</t>
   </si>
   <si>
     <t>2026-03</t>
   </si>
   <si>
-    <t>渠道库存恢复正常</t>
-  </si>
-  <si>
     <t>2026-04</t>
-  </si>
-  <si>
-    <t>春季新品上市</t>
   </si>
   <si>
     <t>2026-05</t>
   </si>
   <si>
-    <t>五一活动提升客流</t>
-  </si>
-  <si>
     <t>2026-06</t>
-  </si>
-  <si>
-    <t>年中大促表现良好</t>
   </si>
   <si>
     <t>2026-07</t>
   </si>
   <si>
-    <t>暑期需求稳步增长</t>
-  </si>
-  <si>
     <t>2026-08</t>
-  </si>
-  <si>
-    <t>重点门店完成升级</t>
-  </si>
-  <si>
-    <t>2026-09</t>
-  </si>
-  <si>
-    <t>开学季拉动零售销量</t>
-  </si>
-  <si>
-    <t>2026-10</t>
-  </si>
-  <si>
-    <t>国庆促销转化率提升</t>
-  </si>
-  <si>
-    <t>2026-11</t>
-  </si>
-  <si>
-    <t>双十一订单集中交付</t>
-  </si>
-  <si>
-    <t>2026-12</t>
-  </si>
-  <si>
-    <t>年度收官冲刺</t>
-  </si>
-  <si>
-    <t>2027-01</t>
-  </si>
-  <si>
-    <t>春节备货周期提前</t>
-  </si>
-  <si>
-    <t>2027-02</t>
-  </si>
-  <si>
-    <t>节后渠道补货</t>
-  </si>
-  <si>
-    <t>2027-03</t>
-  </si>
-  <si>
-    <t>一季度新品推广完成</t>
-  </si>
-  <si>
-    <t>index</t>
-  </si>
-  <si>
-    <t>name</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="#,##0&quot; 万元&quot;"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -530,7 +440,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -564,19 +474,6 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="FF163A59"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF163A59"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF163A59"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top/>
       <bottom style="thin">
@@ -593,15 +490,6 @@
       <bottom style="thin">
         <color rgb="FFD9E2F3"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFD9E2F3"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -728,7 +616,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -740,34 +628,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -853,7 +741,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -861,44 +749,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="2" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="2" fillId="0" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1177,16 +1038,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RegionalSalesTestData" displayName="RegionalSalesTestData" ref="A1:G16" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G16" etc:filterBottomFollowUsedRange="0"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RegionalSalesTestData" displayName="RegionalSalesTestData" ref="A1:D9" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D9" etc:filterBottomFollowUsedRange="0"/>
+  <tableColumns count="4">
     <tableColumn id="1" name="月份"/>
-    <tableColumn id="2" name="华东"/>
-    <tableColumn id="3" name="华南"/>
-    <tableColumn id="4" name="华西"/>
-    <tableColumn id="5" name="华北"/>
-    <tableColumn id="6" name="填报日期"/>
-    <tableColumn id="7" name="备注"/>
+    <tableColumn id="2" name="示例字段1"/>
+    <tableColumn id="3" name="示例字段2"/>
+    <tableColumn id="4" name="示例字段3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1387,16 +1245,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="2" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:7">
+    <row r="1" ht="26" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1409,361 +1265,126 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:4">
+      <c r="A2" s="3">
+        <v>46023</v>
+      </c>
+      <c r="B2" s="4">
+        <v>86</v>
+      </c>
+      <c r="C2" s="4">
+        <v>62</v>
+      </c>
+      <c r="D2" s="4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:4">
+      <c r="A3" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B3" s="4">
+        <v>104</v>
+      </c>
+      <c r="C3" s="4">
+        <v>75</v>
+      </c>
+      <c r="D3" s="4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:4">
+      <c r="A4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="B4" s="4">
+        <v>98</v>
+      </c>
+      <c r="C4" s="4">
+        <v>81</v>
+      </c>
+      <c r="D4" s="4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:4">
+      <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="B5" s="4">
+        <v>126</v>
+      </c>
+      <c r="C5" s="4">
+        <v>90</v>
+      </c>
+      <c r="D5" s="4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:4">
+      <c r="A6" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="B6" s="4">
+        <v>142</v>
+      </c>
+      <c r="C6" s="4">
+        <v>96</v>
+      </c>
+      <c r="D6" s="4">
+        <v>80</v>
+      </c>
     </row>
-    <row r="2" ht="22" customHeight="1" spans="1:7">
-      <c r="A2" s="4" t="s">
+    <row r="7" ht="22" customHeight="1" spans="1:4">
+      <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5">
-        <v>86</v>
-      </c>
-      <c r="C2" s="5">
-        <v>62</v>
-      </c>
-      <c r="D2" s="5">
-        <v>48</v>
-      </c>
-      <c r="E2" s="5">
-        <v>71</v>
-      </c>
-      <c r="F2" s="6">
-        <v>46053</v>
-      </c>
-      <c r="G2" s="7" t="s">
+      <c r="B7" s="4">
+        <v>158</v>
+      </c>
+      <c r="C7" s="4">
+        <v>112</v>
+      </c>
+      <c r="D7" s="4">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:4">
+      <c r="A8" s="6" t="s">
         <v>8</v>
       </c>
+      <c r="B8" s="4">
+        <v>149</v>
+      </c>
+      <c r="C8" s="4">
+        <v>118</v>
+      </c>
+      <c r="D8" s="4">
+        <v>92</v>
+      </c>
     </row>
-    <row r="3" ht="22" customHeight="1" spans="1:7">
-      <c r="A3" s="8" t="s">
+    <row r="9" ht="22" customHeight="1" spans="1:4">
+      <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="9">
-        <v>104</v>
-      </c>
-      <c r="C3" s="9">
-        <v>75</v>
-      </c>
-      <c r="D3" s="9">
-        <v>56</v>
-      </c>
-      <c r="E3" s="9">
-        <v>68</v>
-      </c>
-      <c r="F3" s="10">
-        <v>46081</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>10</v>
+      <c r="B9" s="4">
+        <v>163</v>
+      </c>
+      <c r="C9" s="4">
+        <v>124</v>
+      </c>
+      <c r="D9" s="4">
+        <v>97</v>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1" spans="1:7">
-      <c r="A4" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="9">
-        <v>98</v>
-      </c>
-      <c r="C4" s="9">
-        <v>81</v>
-      </c>
-      <c r="D4" s="9">
-        <v>64</v>
-      </c>
-      <c r="E4" s="9">
-        <v>77</v>
-      </c>
-      <c r="F4" s="10">
-        <v>46112</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:7">
-      <c r="A5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="9">
-        <v>126</v>
-      </c>
-      <c r="C5" s="9">
-        <v>90</v>
-      </c>
-      <c r="D5" s="9">
-        <v>72</v>
-      </c>
-      <c r="E5" s="9">
-        <v>85</v>
-      </c>
-      <c r="F5" s="10">
-        <v>46142</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1" spans="1:7">
-      <c r="A6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="9">
-        <v>142</v>
-      </c>
-      <c r="C6" s="9">
-        <v>96</v>
-      </c>
-      <c r="D6" s="9">
-        <v>80</v>
-      </c>
-      <c r="E6" s="9">
-        <v>91</v>
-      </c>
-      <c r="F6" s="10">
-        <v>46173</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1" spans="1:7">
-      <c r="A7" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="9">
-        <v>158</v>
-      </c>
-      <c r="C7" s="9">
-        <v>112</v>
-      </c>
-      <c r="D7" s="9">
-        <v>88</v>
-      </c>
-      <c r="E7" s="9">
-        <v>103</v>
-      </c>
-      <c r="F7" s="10">
-        <v>46203</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1" spans="1:7">
-      <c r="A8" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="9">
-        <v>149</v>
-      </c>
-      <c r="C8" s="9">
-        <v>118</v>
-      </c>
-      <c r="D8" s="9">
-        <v>92</v>
-      </c>
-      <c r="E8" s="9">
-        <v>109</v>
-      </c>
-      <c r="F8" s="10">
-        <v>46234</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="1:7">
-      <c r="A9" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="9">
-        <v>163</v>
-      </c>
-      <c r="C9" s="9">
-        <v>124</v>
-      </c>
-      <c r="D9" s="9">
-        <v>97</v>
-      </c>
-      <c r="E9" s="9">
-        <v>115</v>
-      </c>
-      <c r="F9" s="10">
-        <v>46265</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="1:7">
-      <c r="A10" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="9">
-        <v>171</v>
-      </c>
-      <c r="C10" s="9">
-        <v>129</v>
-      </c>
-      <c r="D10" s="9">
-        <v>101</v>
-      </c>
-      <c r="E10" s="9">
-        <v>121</v>
-      </c>
-      <c r="F10" s="10">
-        <v>46295</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="1:7">
-      <c r="A11" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="9">
-        <v>184</v>
-      </c>
-      <c r="C11" s="9">
-        <v>137</v>
-      </c>
-      <c r="D11" s="9">
-        <v>108</v>
-      </c>
-      <c r="E11" s="9">
-        <v>128</v>
-      </c>
-      <c r="F11" s="10">
-        <v>46326</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="1:7">
-      <c r="A12" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="9">
-        <v>196</v>
-      </c>
-      <c r="C12" s="9">
-        <v>145</v>
-      </c>
-      <c r="D12" s="9">
-        <v>116</v>
-      </c>
-      <c r="E12" s="9">
-        <v>136</v>
-      </c>
-      <c r="F12" s="10">
-        <v>46356</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="1:7">
-      <c r="A13" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="9">
-        <v>212</v>
-      </c>
-      <c r="C13" s="9">
-        <v>153</v>
-      </c>
-      <c r="D13" s="9">
-        <v>124</v>
-      </c>
-      <c r="E13" s="9">
-        <v>149</v>
-      </c>
-      <c r="F13" s="10">
-        <v>46387</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="1:7">
-      <c r="A14" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="9">
-        <v>193</v>
-      </c>
-      <c r="C14" s="9">
-        <v>141</v>
-      </c>
-      <c r="D14" s="9">
-        <v>119</v>
-      </c>
-      <c r="E14" s="9">
-        <v>143</v>
-      </c>
-      <c r="F14" s="10">
-        <v>46418</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1" spans="1:7">
-      <c r="A15" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="9">
-        <v>181</v>
-      </c>
-      <c r="C15" s="9">
-        <v>136</v>
-      </c>
-      <c r="D15" s="9">
-        <v>113</v>
-      </c>
-      <c r="E15" s="9">
-        <v>138</v>
-      </c>
-      <c r="F15" s="10">
-        <v>46446</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1" spans="1:7">
-      <c r="A16" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="13">
-        <v>205</v>
-      </c>
-      <c r="C16" s="13">
-        <v>157</v>
-      </c>
-      <c r="D16" s="13">
-        <v>129</v>
-      </c>
-      <c r="E16" s="13">
-        <v>151</v>
-      </c>
-      <c r="F16" s="14">
-        <v>46477</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>36</v>
-      </c>
-    </row>
+    <row r="10" ht="22" customHeight="1"/>
+    <row r="11" ht="22" customHeight="1"/>
+    <row r="12" ht="22" customHeight="1"/>
+    <row r="13" ht="22" customHeight="1"/>
+    <row r="14" ht="22" customHeight="1"/>
+    <row r="15" ht="22" customHeight="1"/>
+    <row r="16" ht="22" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -1771,176 +1392,4 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultColWidth="8.94117647058824" defaultRowHeight="16.8" outlineLevelCol="1"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>